--- a/data/trans_bre/POLIPATOLOGIA_Lim_2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_2-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,17; 19,84</t>
+          <t>10,42; 19,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 17,28</t>
+          <t>8,73; 17,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 12,21</t>
+          <t>1,01; 12,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,49; 122,31</t>
+          <t>51,88; 119,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,24; 131,59</t>
+          <t>52,94; 137,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 58,22</t>
+          <t>4,16; 59,68</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 16,77</t>
+          <t>8,87; 16,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 14,69</t>
+          <t>7,3; 14,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,7; 26,66</t>
+          <t>14,22; 25,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,04; 112,16</t>
+          <t>46,89; 109,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,76; 111,96</t>
+          <t>43,58; 110,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,74; 427,69</t>
+          <t>85,66; 348,43</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 14,93</t>
+          <t>6,51; 14,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 13,68</t>
+          <t>5,95; 13,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 15,56</t>
+          <t>-6,92; 15,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40,15; 121,14</t>
+          <t>37,32; 118,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,18; 112,14</t>
+          <t>38,87; 112,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 96,83</t>
+          <t>-35,1; 92,63</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 14,74</t>
+          <t>7,03; 14,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 13,89</t>
+          <t>6,72; 13,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 16,78</t>
+          <t>5,75; 16,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,86; 93,63</t>
+          <t>34,56; 94,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,24; 102,37</t>
+          <t>38,59; 97,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,17; 98,06</t>
+          <t>29,36; 98,37</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,24; 14,28</t>
+          <t>10,23; 14,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,76</t>
+          <t>8,87; 12,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 16,01</t>
+          <t>7,17; 15,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56,77; 87,87</t>
+          <t>56,82; 88,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,81; 89,65</t>
+          <t>55,23; 91,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,15; 110,98</t>
+          <t>41,82; 109,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_Lim_2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_2-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>9,7</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 19,22</t>
+          <t>10,27; 19,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,73; 17,95</t>
+          <t>8,04; 17,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 12,69</t>
+          <t>5,96; 14,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,88; 119,75</t>
+          <t>51,63; 125,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,94; 137,53</t>
+          <t>45,7; 132,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 59,68</t>
+          <t>22,94; 69,1</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,95</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>152,03%</t>
+          <t>101,17%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 16,84</t>
+          <t>8,76; 16,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 14,77</t>
+          <t>7,42; 14,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,22; 25,52</t>
+          <t>12,24; 18,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,89; 109,94</t>
+          <t>46,16; 107,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,58; 110,46</t>
+          <t>44,25; 107,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,66; 348,43</t>
+          <t>69,68; 136,62</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>14,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 14,83</t>
+          <t>6,6; 15,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,68</t>
+          <t>5,35; 13,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 15,28</t>
+          <t>10,91; 18,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,32; 118,13</t>
+          <t>38,39; 120,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,87; 112,76</t>
+          <t>35,32; 116,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 92,63</t>
+          <t>56,81; 129,46</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,91</t>
+          <t>15,09</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>81,2%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 14,8</t>
+          <t>6,71; 14,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,74</t>
+          <t>6,79; 14,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 16,91</t>
+          <t>11,67; 18,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,56; 94,01</t>
+          <t>34,17; 92,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,59; 97,85</t>
+          <t>39,53; 103,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,36; 98,37</t>
+          <t>57,06; 109,75</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,42</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,23; 14,16</t>
+          <t>10,12; 14,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,87; 12,86</t>
+          <t>8,64; 12,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,97</t>
+          <t>12,39; 16,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56,82; 88,56</t>
+          <t>55,85; 88,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,23; 91,31</t>
+          <t>54,63; 89,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,82; 109,93</t>
+          <t>64,79; 95,08</t>
         </is>
       </c>
     </row>
